--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/nuble.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M298"/>
+  <dimension ref="A1:M299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2144.22</v>
+        <v>2126.06</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2268.67</v>
+        <v>2246.03</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24883.62</v>
+        <v>24623.03</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7628.16</v>
+        <v>7543.17</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2719.57</v>
+        <v>2704.68</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14599.12</v>
+        <v>14580.54</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4204.7</v>
+        <v>4199.35</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5946.96</v>
+        <v>5939.39</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6512.32</v>
+        <v>6535.56</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3920.23</v>
+        <v>3962.87</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7680.98</v>
+        <v>7813.56</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4107.76</v>
+        <v>4126.89</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3086.31</v>
+        <v>3108.56</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3691.23</v>
+        <v>3684.69</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2237.69</v>
+        <v>2233.73</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4110.39</v>
+        <v>4103.1</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4285.57</v>
+        <v>4278.93</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1827.7</v>
+        <v>1837.14</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3206.06</v>
+        <v>3228.69</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3723.81</v>
+        <v>3750.09</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4067.15</v>
+        <v>4095.85</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2294.84</v>
+        <v>2265.17</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2164.6</v>
+        <v>2136.62</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8867.709999999999</v>
+        <v>8755.07</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5082.84</v>
+        <v>5018.27</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>810.16</v>
+        <v>799.87</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4244.17</v>
+        <v>4228.95</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4276.81</v>
+        <v>4261.48</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15967.45</v>
+        <v>15910.2</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3612.78</v>
+        <v>3599.82</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>28236.83</v>
+        <v>28175.72</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3899.18</v>
+        <v>3890.74</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5659.04</v>
+        <v>5593.55</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>20506.74</v>
+        <v>20269.41</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4336.62</v>
+        <v>4299.89</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3768.88</v>
+        <v>3765.85</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>957.49</v>
+        <v>961.83</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2387.15</v>
+        <v>2397.97</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1382.82</v>
+        <v>1389.09</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1111.85</v>
+        <v>1116.89</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>14620.37</v>
+        <v>14686.62</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3798.6</v>
+        <v>3815.82</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2000.31</v>
+        <v>2009.37</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1693.44</v>
+        <v>1697.93</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>834.2</v>
+        <v>836.41</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>11301.47</v>
+        <v>11331.44</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1866.67</v>
+        <v>1871.62</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6034.93</v>
+        <v>6050.93</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1751.52</v>
+        <v>1749.06</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1401.5</v>
+        <v>1403.3</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2161.22</v>
+        <v>2179.69</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10165.68</v>
+        <v>10252.55</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2961.27</v>
+        <v>2999.33</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2008.74</v>
+        <v>2019.73</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>10597.72</v>
+        <v>10655.67</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5267.97</v>
+        <v>5133.45</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7846.56</v>
+        <v>7663</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2396.67</v>
+        <v>2366.25</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3482.76</v>
+        <v>3432.57</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9221.93</v>
+        <v>9102.75</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3868.82</v>
+        <v>3818.82</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2402.2</v>
+        <v>2397.47</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10096.91</v>
+        <v>10096.97</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2822.92</v>
+        <v>2822.94</v>
       </c>
     </row>
     <row r="66">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>790.13</v>
+        <v>791.23</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5616.1</v>
+        <v>5623.9</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4836.65</v>
+        <v>4843.36</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3199.47</v>
+        <v>3197.28</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2396.97</v>
+        <v>2395.33</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>32924.84</v>
+        <v>32750.91</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>944.14</v>
+        <v>938.23</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5267.97</v>
+        <v>5234.96</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4859.88</v>
+        <v>4891.74</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4122.62</v>
+        <v>4149.64</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9513.1</v>
+        <v>9641.209999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3956.06</v>
+        <v>4009.33</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4742.39</v>
+        <v>4814.59</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2502.23</v>
+        <v>2540.32</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2595.22</v>
+        <v>2634.73</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1966.38</v>
+        <v>2014.2</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2827.87</v>
+        <v>2896.63</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>813.7</v>
+        <v>833.49</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3499.46</v>
+        <v>3584.56</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2543.14</v>
+        <v>2604.98</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7865.04</v>
+        <v>8056.3</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2863.19</v>
+        <v>2932.81</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>10109.4</v>
+        <v>10355.24</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>10047.14</v>
+        <v>10291.46</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7846.57</v>
+        <v>8044.93</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>10155.51</v>
+        <v>10457.36</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3826.79</v>
+        <v>3813.16</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8290.639999999999</v>
+        <v>8228.6</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>44984.98</v>
+        <v>45115.3</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>76561.25</v>
+        <v>76783.05</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2683.24</v>
+        <v>2697.1</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3454.47</v>
+        <v>3472.32</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5397.12</v>
+        <v>5374.36</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1173.68</v>
+        <v>1184.36</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1846.87</v>
+        <v>1863.67</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2142.2</v>
+        <v>2157.11</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>868.0599999999999</v>
+        <v>874.1</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>20530.4</v>
+        <v>20665.61</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2200.48</v>
+        <v>2214.97</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1905.06</v>
+        <v>1922.03</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3554.18</v>
+        <v>3548.09</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2244.89</v>
+        <v>2241.04</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1288.66</v>
+        <v>1287.33</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2550.99</v>
+        <v>2532.71</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2668.6</v>
+        <v>2649.49</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2438.48</v>
+        <v>2434.89</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>969.09</v>
+        <v>963.8099999999999</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3231.6</v>
+        <v>3212.56</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>910.99</v>
+        <v>905.62</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4280.45</v>
+        <v>4254.44</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2700.28</v>
+        <v>2689.86</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2434.75</v>
+        <v>2425.35</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5402.09</v>
+        <v>5381.24</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3439.54</v>
+        <v>3457.35</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2783.32</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1562.43</v>
+        <v>1631.43</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1683.65</v>
+        <v>1758.01</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>913.01</v>
+        <v>939.53</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7003.07</v>
+        <v>7030.68</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3089.74</v>
+        <v>3049.96</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1808.36</v>
+        <v>1841.15</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5117.86</v>
+        <v>5210.65</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3410.49</v>
+        <v>3463.91</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>14682.21</v>
+        <v>14681.45</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1640.99</v>
+        <v>1633.65</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1859.97</v>
+        <v>1851.65</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1242.91</v>
+        <v>1243.98</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2197.75</v>
+        <v>2199.64</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2779.17</v>
+        <v>2790.65</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4067.4</v>
+        <v>4084.2</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2663.91</v>
+        <v>2656.56</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1246.82</v>
+        <v>1243.38</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1152.69</v>
+        <v>1139.39</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>987.4400000000001</v>
+        <v>976.05</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7563.17</v>
+        <v>7475.86</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2189.33</v>
+        <v>2156.68</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>6788.4</v>
+        <v>6687.15</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>813.17</v>
+        <v>801.04</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2675.89</v>
+        <v>2635.98</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1352.64</v>
+        <v>1343.97</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1664.84</v>
+        <v>1654.17</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1315.78</v>
+        <v>1307.35</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1200.81</v>
+        <v>1195.64</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>786.3</v>
+        <v>782.91</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>771.09</v>
+        <v>767.77</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5922.02</v>
+        <v>5896.51</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3412.56</v>
+        <v>3397.86</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>15974.83</v>
+        <v>15906.01</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5117.86</v>
+        <v>5043.82</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>16458.87</v>
+        <v>16075.88</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5149.43</v>
+        <v>5029.61</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3593.25</v>
+        <v>3509.64</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4156.72</v>
+        <v>4024.17</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2582.98</v>
+        <v>2500.62</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1901.99</v>
+        <v>1867.5</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>8625.85</v>
+        <v>8469.42</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3164.1</v>
+        <v>3079.38</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1648.85</v>
+        <v>1604.7</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>7657.76</v>
+        <v>7452.71</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>4257.22</v>
+        <v>4269.61</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3534.25</v>
+        <v>3544.54</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4990.68</v>
+        <v>5005.21</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1950.8</v>
+        <v>1967.36</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2482.26</v>
+        <v>2503.33</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3457.99</v>
+        <v>3452.21</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>852.59</v>
+        <v>851.17</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>939.33</v>
+        <v>937.76</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2415.71</v>
+        <v>2445.45</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1030.23</v>
+        <v>1043.67</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1099.15</v>
+        <v>1126.2</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>20230.97</v>
+        <v>20613.59</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5186.3</v>
+        <v>5284.39</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3215</v>
+        <v>3251.56</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>5342.83</v>
+        <v>5403.59</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1400.65</v>
+        <v>1409.61</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>33140.46</v>
+        <v>33352.42</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>5555.99</v>
+        <v>5573.47</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1056.04</v>
+        <v>1059.37</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1352.44</v>
+        <v>1358.04</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6693.24</v>
+        <v>6720.98</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>4675.95</v>
+        <v>4695.33</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>783.95</v>
+        <v>785.5700000000001</v>
       </c>
     </row>
     <row r="189">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>17765.52</v>
+        <v>17802.32</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4594-351-CM26</t>
+          <t>4707-139-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.140.802-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>924.42</v>
+        <v>1836.34</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4707-139-CM26</t>
+          <t>4594-351-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.140.802-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1832.54</v>
+        <v>926.34</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>796.6900000000001</v>
+        <v>798.34</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>7930.41</v>
+        <v>7896.35</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>979.46</v>
+        <v>975.25</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2502.25</v>
+        <v>2468.23</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2454.58</v>
+        <v>2421.21</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>10712.67</v>
+        <v>10567.03</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>5187.74</v>
+        <v>5117.21</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>937.6</v>
+        <v>929.61</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>9749.209999999999</v>
+        <v>9666.059999999999</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1809.58</v>
+        <v>1794.15</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1458.47</v>
+        <v>1446.03</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>994.78</v>
+        <v>986.3</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3016.1</v>
+        <v>2990.38</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2355.44</v>
+        <v>2373.28</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3838.19</v>
+        <v>3867.26</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1493.5</v>
+        <v>1504.81</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1931.69</v>
+        <v>1946.32</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>788.98</v>
+        <v>791.97</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>10390.44</v>
+        <v>10364.21</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2723.37</v>
+        <v>2716.5</v>
       </c>
     </row>
     <row r="212">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5044.06</v>
+        <v>5091.98</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2724-348-CM26</t>
+          <t>1057513-257-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2950.14</v>
+        <v>3000.53</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4594-422-CM26</t>
+          <t>2724-348-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5432.33</v>
+        <v>2972.12</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1057513-257-CM26</t>
+          <t>4594-422-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13527,17 +13527,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2978.34</v>
+        <v>5472.8</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>5187.74</v>
+        <v>5165</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3563.39</v>
+        <v>3524.63</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4406.23</v>
+        <v>4396.23</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3876.09</v>
+        <v>3895.13</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>871.78</v>
+        <v>876.0599999999999</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2107.17</v>
+        <v>2114.16</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>844.7</v>
+        <v>849.1900000000001</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>8354.709999999999</v>
+        <v>8452.709999999999</v>
       </c>
     </row>
     <row r="224">
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3042.36</v>
+        <v>3073.3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1057511-725-CM26</t>
+          <t>1057506-4123-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14142,12 +14142,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>MG Publicidad y Eventos SpA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>76.202.065-3</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4017.95</v>
+        <v>3824.06</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1057506-4123-CM26</t>
+          <t>1057511-725-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.202.065-3</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3785.57</v>
+        <v>4058.81</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>17166.73</v>
+        <v>17327.74</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>4027.46</v>
+        <v>4065.23</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1590.21</v>
+        <v>1605.13</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1096.31</v>
+        <v>1106.59</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>5405.68</v>
+        <v>5456.38</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>35614.15</v>
+        <v>35343.98</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2462.26</v>
+        <v>2420.66</v>
       </c>
     </row>
     <row r="234">
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3971.96</v>
+        <v>3915.59</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3674-341-CM26</t>
+          <t>1072229-102-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SPB SOCIEDAD COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.743.864-6</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>5467.72</v>
+        <v>1164.56</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1072229-102-CM26</t>
+          <t>3674-341-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ilustre Municipalidad de Chillan Viejo</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>SPB SOCIEDAD COMERCIAL SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>77.743.864-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1181.33</v>
+        <v>5390.12</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1294.76</v>
+        <v>1276.97</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1740.08</v>
+        <v>1716.17</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1733.23</v>
+        <v>1722.48</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1192.91</v>
+        <v>1198.32</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1212.22</v>
+        <v>1217.73</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1005.26</v>
+        <v>1020.23</v>
       </c>
     </row>
     <row r="243">
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1163.5</v>
+        <v>1180.83</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1057508-1842-CM26</t>
+          <t>1057508-1841-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>89.842.300-k</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1371.21</v>
+        <v>9177.940000000001</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1057508-1841-CM26</t>
+          <t>1057508-1842-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>89.842.300-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>9043.280000000001</v>
+        <v>1391.63</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>12681.03</v>
+        <v>12768.58</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3602.75</v>
+        <v>3613.89</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2716</v>
+        <v>2708.82</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1323.84</v>
+        <v>1320.34</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>9217.280000000001</v>
+        <v>9094.5</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4272.69</v>
+        <v>4189.06</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2515.25</v>
+        <v>2466.01</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5154.74</v>
+        <v>5053.84</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>5326.24</v>
+        <v>5221.99</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>6499.15</v>
+        <v>6560.89</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1599.43</v>
+        <v>1614.62</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4982.69</v>
+        <v>5002.14</v>
       </c>
     </row>
     <row r="258">
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2089.2</v>
+        <v>2110.21</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3871-137-CM26</t>
+          <t>1057510-2524-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>72.632.100-0</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Municipalidad de Pemuco - Salud</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>777.1</v>
+        <v>7212.04</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1057510-2524-CM26</t>
+          <t>3871-136-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16277,12 +16277,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>72.632.100-0</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>Municipalidad de Pemuco - Salud</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>7140.22</v>
+        <v>2018.83</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3871-136-CM26</t>
+          <t>3871-137-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1998.73</v>
+        <v>784.92</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2786.28</v>
+        <v>2814.3</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3046.33</v>
+        <v>3076.83</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>35308.25</v>
+        <v>35661.81</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2321.35</v>
+        <v>2344.59</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>8575.540000000001</v>
+        <v>8619.24</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>936.67</v>
+        <v>940.3099999999999</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>853.6900000000001</v>
+        <v>849.37</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>963.83</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1989.53</v>
+        <v>1993.77</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1004.69</v>
+        <v>1011.24</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>784.28</v>
+        <v>789.39</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1041.76</v>
+        <v>1048.55</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>6364.27</v>
+        <v>6405.76</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>20732.49</v>
+        <v>20780.03</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2739.59</v>
+        <v>2757.93</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>4884.49</v>
+        <v>4918.67</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1259.47</v>
+        <v>1268.29</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2438.58</v>
+        <v>2430.88</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1002.56</v>
+        <v>1000.38</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3071.04</v>
+        <v>3064.36</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>11117.85</v>
+        <v>11095.56</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>812.1900000000001</v>
+        <v>810.5599999999999</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>847.26</v>
+        <v>845.5599999999999</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4667.19</v>
+        <v>4657.83</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>4659.17</v>
+        <v>4632.2</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4338.72</v>
+        <v>4268.7</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2952.25</v>
+        <v>2904.61</v>
       </c>
     </row>
     <row r="289">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>16149.05</v>
+        <v>15890.12</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1057506-4387-CM26</t>
+          <t>1043046-78-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18102,17 +18102,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>62.000.450-2</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1682.59</v>
+        <v>767.8200000000001</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1043046-78-CM26</t>
+          <t>1049242-43-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18168,12 +18168,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>62.000.450-2</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+          <t>Secretaria Regional Ministerial de las Artes y el</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>776.86</v>
+        <v>3462.33</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1049242-43-CM26</t>
+          <t>1057506-4387-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18224,17 +18224,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Secretaria Regional Ministerial de las Artes y el</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18244,12 +18244,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3503.09</v>
+        <v>1663.02</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2646.08</v>
+        <v>2633.07</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1603.21</v>
+        <v>1595.33</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2146.99</v>
+        <v>2136.44</v>
       </c>
     </row>
     <row r="296">
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>4877.75</v>
+        <v>4853.77</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2467-880-CM26</t>
+          <t>229-546-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18534,12 +18534,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>6654.46</v>
+        <v>12926.44</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>229-546-CM26</t>
+          <t>2467-880-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18595,12 +18595,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18610,12 +18610,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18625,7 +18625,68 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>12840.49</v>
+        <v>6699</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>4329-495-CM26</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>69.140.600-8</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Ñiquen</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="n">
+        <v>1053.89</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/nuble.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/nuble.xlsx
@@ -562,7 +562,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2549,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2675,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2801,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3118,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>77.550.346-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3370,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3435,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3561,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3813,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3878,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3943,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4008,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4134,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4577,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4642,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4837,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4967,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5288,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5536,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5723,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5788,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5853,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5918,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5983,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6113,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6239,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6304,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6369,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6499,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6564,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6629,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6694,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6759,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6885,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7076,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7141,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7206,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7336,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7401,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7466,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7531,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7596,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7726,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8100,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8165,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8417,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8482,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8608,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8673,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8860,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8925,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8990,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9116,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9181,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9433,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9498,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9563,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9811,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9876,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9941,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10189,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10254,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10319,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10384,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10575,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10640,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10827,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10892,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10957,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11022,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11087,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11461,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11526,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11591,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11656,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11721,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12034,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12160,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12412,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12477,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12603,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12668,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12794,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12981,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13046,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13111,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13237,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13302,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13428,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13554,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13680,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13806,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13871,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13997,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14184,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14249,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14562,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14627,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14822,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14887,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14952,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15017,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15082,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15212,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15338,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15403,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15529,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15594,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15659,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15785,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16106,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16358,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16423,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16549,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16679,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16744,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16809,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16874,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16939,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17004,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17130,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17390,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17455,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17520,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17646,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17772,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17837,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17902,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17967,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18032,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18097,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18162,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18227,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18292,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18357,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18422,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18487,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18552,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18678,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18743,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18808,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18873,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19060,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19125,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19251,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19316,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19381,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19446,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19511,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19576,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19641,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19706,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19771,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19897,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19962,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20027,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20092,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20157,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20222,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20287,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20352,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20417,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20482,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20547,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20612,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20677,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20742,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20807,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20872,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20937,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21063,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21128,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21193,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21258,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21323,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21449,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21514,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21579,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21705,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21770,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21896,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21961,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22026,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22091,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22217,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22282,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22347,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22412,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22538,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22603,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22668,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22794,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22981,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23046,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23237,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23302,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23367,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23432,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23497,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23562,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23627,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23692,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23944,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24009,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24135,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24200,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24265,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24391,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24456,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24643,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24708,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24773,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24899,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24964,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25216,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25281,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25346,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25411,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25476,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25541,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25606,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25671,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25736,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25996,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26061,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26126,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26191,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26256,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26321,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26447,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26638,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26703,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26894,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26959,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27024,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27089,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27154,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27345,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27662,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27727,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27792,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27918,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27983,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28048,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28239,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28369,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28434,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28499,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28564,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28755,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28820,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28885,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28950,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29015,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29141,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29328,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29393,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29458,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29588,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29718,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29913,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29978,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30043,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30108,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30173,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30238,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30303,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30429,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30799,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30864,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30929,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30994,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31120,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31246,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31372,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31437,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31502,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31632,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31758,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31823,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31888,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31953,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32018,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32083,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32148,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32213,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32278,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32343,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32408,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32473,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32538,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32603,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32729,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32855,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33042,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33233,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33298,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33363,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33489,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33554,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33619,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33684,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33810,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33940,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34005,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34131,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34196,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34326,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34391,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34521,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34586,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34716,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34781,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34846,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35033,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35098,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35163,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35228,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35293,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35358,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35549,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35679,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35744,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35809,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35874,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35939,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36065,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36130,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36260,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36325,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36390,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36455,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +36650,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36715,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36780,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36845,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36910,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36975,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +37040,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37231,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37296,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37361,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37426,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37491,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37556,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37621,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +37686,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37751,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37877,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37942,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38068,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38133,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38259,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38324,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38389,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38454,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38519,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +38584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38649,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +38844,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38909,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38974,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +39039,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39104,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39417,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39482,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39547,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39612,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39677,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39742,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +39868,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39933,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39998,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +40063,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40189,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +40254,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +40319,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40384,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +40510,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +40575,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +40701,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +40766,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +40831,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +40957,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +41022,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +41209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41335,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41400,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41526,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41656,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41721,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +41786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +41851,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +41916,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +42046,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42111,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42176,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42306,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/nuble.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/nuble.xlsx
@@ -1269,7 +1269,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1460,7 +1464,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1777,7 +1785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2098,7 +2110,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2614,7 +2630,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2740,7 +2760,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2931,7 +2955,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3309,7 +3337,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3500,7 +3532,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3626,7 +3662,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4516,7 +4556,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5162,7 +5206,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7917,7 +7965,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8356,7 +8408,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10006,7 +10062,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10067,7 +10127,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10128,7 +10192,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +11919,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12045,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13493,7 +13569,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13619,7 +13699,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13936,7 +14020,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14123,7 +14211,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15277,7 +15369,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15980,7 +16076,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16236,7 +16336,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16297,7 +16401,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +17693,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +17823,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18999,7 +19115,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19190,7 +19310,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21002,7 +21126,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21835,7 +21963,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22733,7 +22865,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22859,7 +22995,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22920,7 +23060,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23883,7 +24027,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24074,7 +24222,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24521,7 +24673,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24582,7 +24738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24838,7 +24998,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25155,7 +25319,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26768,7 +26936,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +27456,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27540,7 +27716,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28178,7 +28358,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28694,7 +28878,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29080,7 +29268,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29206,7 +29398,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29267,7 +29463,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30368,7 +30568,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30494,7 +30698,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30555,7 +30763,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30677,7 +30889,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31059,7 +31275,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32794,7 +33014,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32920,7 +33144,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32981,7 +33209,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33172,7 +33404,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34911,7 +35147,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35423,7 +35663,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36004,7 +36248,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37816,7 +38064,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38007,7 +38259,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39169,7 +39425,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40128,7 +40388,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40449,7 +40713,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40896,7 +41164,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41087,7 +41359,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41274,7 +41550,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
